--- a/output/pdf_financials_xlsx/NMI.xlsx
+++ b/output/pdf_financials_xlsx/NMI.xlsx
@@ -1057,16 +1057,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2.997606</v>
+        <v>-2.997606</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3.011009</v>
+        <v>-3.011009</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.624478</v>
+        <v>-1.624478</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.229676</v>
+        <v>-1.229676</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0.08667999999999999</v>
@@ -1277,16 +1277,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.997606</v>
+        <v>-2.997606</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3.011009</v>
+        <v>-3.011009</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.624478</v>
+        <v>-1.624478</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.229676</v>
+        <v>-1.229676</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>0.08667999999999999</v>
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.997606</v>
+        <v>-2.997606</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3.011009</v>
+        <v>-3.011009</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.624478</v>
+        <v>-1.624478</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.229676</v>
+        <v>-1.229676</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>0.08667999999999999</v>
@@ -1535,16 +1535,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>74.94015</v>
+        <v>-74.94015</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>75.27522500000001</v>
+        <v>-75.27522500000001</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>81.2239</v>
+        <v>-81.2239</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>61.4838</v>
+        <v>-61.4838</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.997606</v>
+        <v>-2.997606</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3.011009</v>
+        <v>-3.011009</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.624478</v>
+        <v>-1.624478</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.229676</v>
+        <v>-1.229676</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0.08667999999999999</v>
@@ -1678,16 +1678,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.000648</v>
+        <v>-2.994564</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3.014051</v>
+        <v>-3.007967</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.625492</v>
+        <v>-1.623464</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.229676</v>
+        <v>-1.229676</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0.08667999999999999</v>
@@ -1788,16 +1788,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
@@ -20456,10 +20456,10 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>1.624478</v>
+        <v>-1.624478</v>
       </c>
       <c r="H191" s="5" t="n">
-        <v>1.229676</v>
+        <v>-1.229676</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -21421,10 +21421,10 @@
         </is>
       </c>
       <c r="F204" s="5" t="n">
-        <v>3.011009</v>
+        <v>-3.011009</v>
       </c>
       <c r="G204" s="5" t="n">
-        <v>1.624478</v>
+        <v>-1.624478</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -22414,10 +22414,10 @@
         </is>
       </c>
       <c r="E217" s="5" t="n">
-        <v>2.997606</v>
+        <v>-2.997606</v>
       </c>
       <c r="F217" s="5" t="n">
-        <v>3.011009</v>
+        <v>-3.011009</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NMI.xlsx
+++ b/output/pdf_financials_xlsx/NMI.xlsx
@@ -885,40 +885,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.153605</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.086502</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.042166</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005818</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.005913</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.052037</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.020307</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.003454</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.010069</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.010704</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.018352</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.016927</v>
       </c>
     </row>
     <row r="13">
@@ -1592,40 +1592,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.997606</v>
+        <v>-2.844001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.011009</v>
+        <v>-2.924507</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.624478</v>
+        <v>-1.582312</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.229676</v>
+        <v>-1.223858</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.08667999999999999</v>
+        <v>0.08076700000000001</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.700172</v>
+        <v>-1.752209</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.708928</v>
+        <v>-0.729235</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.473973</v>
+        <v>-5.477427</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.651709</v>
+        <v>-0.661778</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.368654</v>
+        <v>-2.379358</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.582313</v>
+        <v>-0.600665</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.809276</v>
+        <v>-0.826203</v>
       </c>
     </row>
     <row r="28">
@@ -1678,40 +1678,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.994564</v>
+        <v>-2.840959</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.007967</v>
+        <v>-2.921465</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.623464</v>
+        <v>-1.581298</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.229676</v>
+        <v>-1.223858</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.08667999999999999</v>
+        <v>0.08076700000000001</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.700172</v>
+        <v>-1.752209</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.708928</v>
+        <v>-0.729235</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.473973</v>
+        <v>-5.477427</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.651709</v>
+        <v>-0.661778</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.368654</v>
+        <v>-2.379358</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.582313</v>
+        <v>-0.600665</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.809276</v>
+        <v>-0.826203</v>
       </c>
     </row>
     <row r="30">
@@ -1905,19 +1905,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>9.800864000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.313942</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.297938</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.683036</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.096237</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
@@ -1932,13 +1932,13 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.235705</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.252327</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.120481</v>
       </c>
     </row>
     <row r="35">
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>9.800864000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.313942</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.297938</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.683036</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.096237</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
@@ -2018,13 +2018,13 @@
         <v>0</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.235705</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.252327</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.120481</v>
       </c>
     </row>
     <row r="37">
@@ -2507,19 +2507,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>9.913022</v>
+        <v>0.112158</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.421984</v>
+        <v>0.108042</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.343348</v>
+        <v>0.04541</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.727573</v>
+        <v>0.044537</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.133712</v>
+        <v>0.037475</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>2.375046</v>
@@ -2534,13 +2534,13 @@
         <v>1.10986</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.259742</v>
+        <v>0.024037</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.286547</v>
+        <v>0.03422</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.184823</v>
+        <v>0.064342</v>
       </c>
     </row>
     <row r="49">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -18240,7 +18240,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -21334,7 +21334,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -22332,7 +22332,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E216" s="5" t="n">

--- a/output/pdf_financials_xlsx/NMI.xlsx
+++ b/output/pdf_financials_xlsx/NMI.xlsx
@@ -5351,16 +5351,16 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.100516</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001843</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.023716</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
@@ -6392,16 +6392,16 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.100516</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001843</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.023716</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
@@ -6458,7 +6458,7 @@
         <v>0.460762</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.827198</v>
+        <v>-0.8509139999999999</v>
       </c>
       <c r="K135" s="1" t="inlineStr">
         <is>
@@ -12954,7 +12954,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
